--- a/docs/downloads/gsl-indexes/pdf_table_headings.xlsx
+++ b/docs/downloads/gsl-indexes/pdf_table_headings.xlsx
@@ -7,11 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="About" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Index" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="pdf_table_headings" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Index'!$A$1:$H$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'pdf_table_headings'!$A$1:$H$101</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,28 +29,15 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="002E4B70"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D7EFF8"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -76,15 +62,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -451,89 +435,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>GSL PDF Extraction Export</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Index</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>PDF Extraction - Table Headings</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Rows</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>gsl_pdf_extraction_master.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Purpose</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Table labels and captions detected from actual TABLE X.X labels in the CPA PDF.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Caveat</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Generated from PDF font/layout extraction; review before exam reliance.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:H101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -548,3842 +449,3842 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Label</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Content/Text</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Module</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Current Heading</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Book Page</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>PDF Page</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Source Line ID</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>TABLE 1.1</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>TABLE 1.1 Gaining competitive advantage from data</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Building Competitive Advantage on Data</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="G2" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="G2" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>P027-L035</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>TABLE 1.2</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>TABLE 1.2 The leading edge of strategy: fit or stretch</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>STRATEGIC FIT AND STRATEGIC STRETCH</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="G3" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="G3" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>P033-L001</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>TABLE 1.3</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>TABLE 1.3 The three core business types</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Core Business Types</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="G4" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="G4" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>P037-L034</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>TABLE 1.4</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>TABLE 1.4 Core business type typical focus and conflicts</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>How Apple Reshaped the Computer Industry</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="G5" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="G5" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>P038-L030</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>TABLE 1.4</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>TABLE 1.4 Business</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Product innovation</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="G6" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="G6" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>P039-L001</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>TABLE 1.5</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>TABLE 1.5 Driving forces of globalisation</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>1.5 THE GLOBAL CONTEXT OF BUSINESS</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="G7" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="G7" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>P046-L001</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>TABLE 1.6</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>TABLE 1.6 Globalisation risks and considerations for leaders and managers</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>CHALLENGES OF GLOBALISATION</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="G8" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="G8" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>P048-L047</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>TABLE 1.6</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>TABLE 1.6 Risk</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>economic</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Macro- economic</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="F9" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="G9" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="G9" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>P049-L001</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>TABLE 1.7</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>TABLE 1.7 Benefits of globalisation</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>BENEFITS OF GLOBALISATION</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="F10" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="G10" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="G10" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>P051-L001</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>TABLE 1.8</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>TABLE 1.8 Dual roles of managing and leading</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>LEADERSHIP VERSUS MANAGEMENT</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="F11" s="3" t="n">
+      <c r="F11" s="2" t="n">
         <v>54</v>
       </c>
-      <c r="G11" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="G11" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>P054-L004</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>TABLE 1.9</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>TABLE 1.9 Arguments in support of and against leadership</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Great Leader, Poor Manager</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="F12" s="3" t="n">
+      <c r="F12" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="G12" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="G12" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>P055-L026</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>TABLE 1.10</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>TABLE 1.10 Key elements in the role of the strategic leader</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>leaders</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Strategic leaders</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="F13" s="3" t="n">
+      <c r="F13" s="2" t="n">
         <v>56</v>
       </c>
-      <c r="G13" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="G13" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>P056-L027</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>TABLE 1.10</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>TABLE 1.10 Role</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Key elements</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="F14" s="3" t="n">
+      <c r="F14" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="G14" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="G14" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>P057-L001</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>TABLE 1.11</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>TABLE 1.11 Matching the strategy process with transformational leadership</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="F15" s="3" t="n">
+      <c r="F15" s="2" t="n">
         <v>61</v>
       </c>
-      <c r="G15" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="G15" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>P061-L021</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>TABLE 1.12</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>TABLE 1.12 Impact of transformational leadership</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>(discussed in more detail in module 6).</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>QUESTION 1.10</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="F16" s="3" t="n">
+      <c r="F16" s="2" t="n">
         <v>62</v>
       </c>
-      <c r="G16" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="G16" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>P062-L009</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>TABLE 1.13</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>TABLE 1.13 The role of the finance professional in strategy</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>AND LEADERSHIP</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1.9 THE ROLE OF THE CPA IN STRATEGY AND LEADERSHIP</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="F17" s="3" t="n">
+      <c r="F17" s="2" t="n">
         <v>74</v>
       </c>
-      <c r="G17" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="G17" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>P074-L036</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>TABLE 1.13</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>TABLE 1.13 External/internal</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Accountant</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="F18" s="3" t="n">
+      <c r="F18" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="G18" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="G18" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>P075-L001</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>TABLE 1.14</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>TABLE 1.14 Key questions for CPA candidates to consider and answer</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>described in module 1 are included in table 1.14.</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>QUESTION 1.20</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="F19" s="2" t="n">
         <v>76</v>
       </c>
-      <c r="G19" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="G19" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>P076-L007</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>TABLE 1.14</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>TABLE 1.14 Concepts/models/approaches that can be used</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>to answer the key questions</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="F20" s="3" t="n">
+      <c r="F20" s="2" t="n">
         <v>77</v>
       </c>
-      <c r="G20" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="G20" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>P077-L001</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>TABLE 2.1</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>TABLE 2.1 Australian domestic airlines</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Segments in the Australian Domestic Airline Industry</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="F21" s="3" t="n">
+      <c r="F21" s="2" t="n">
         <v>103</v>
       </c>
-      <c r="G21" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="G21" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>P103-L018</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>TABLE 2.2</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>TABLE 2.2 Businesses which utilise a tax agent to submit tax and BAS</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>The Silent Disruption of the Accounting Services Industry</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>94</t>
         </is>
       </c>
-      <c r="F22" s="3" t="n">
+      <c r="F22" s="2" t="n">
         <v>109</v>
       </c>
-      <c r="G22" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="G22" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>P109-L004</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>TABLE 2.3</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>TABLE 2.3 Remote environment analysis worksheet</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Environmental</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>102</t>
         </is>
       </c>
-      <c r="F23" s="3" t="n">
+      <c r="F23" s="2" t="n">
         <v>117</v>
       </c>
-      <c r="G23" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="G23" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>P117-L008</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>TABLE 2.4</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>TABLE 2.4 Remote environment of the luxury goods industry</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Remote Environment Summary for the Luxury Goods Industry</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>113</t>
         </is>
       </c>
-      <c r="F24" s="3" t="n">
+      <c r="F24" s="2" t="n">
         <v>128</v>
       </c>
-      <c r="G24" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="G24" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>P128-L021</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>TABLE 2.4</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>TABLE 2.4 What are the likely issues that have affected and will affect</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>growth (+, = , –)</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>114</t>
         </is>
       </c>
-      <c r="F25" s="3" t="n">
+      <c r="F25" s="2" t="n">
         <v>129</v>
       </c>
-      <c r="G25" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="G25" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>P129-L001</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>TABLE 2.5</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>TABLE 2.5 Basis of competition questions</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>BASIS OF COMPETITION</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>129</t>
         </is>
       </c>
-      <c r="F26" s="3" t="n">
+      <c r="F26" s="2" t="n">
         <v>144</v>
       </c>
-      <c r="G26" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="G26" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>P144-L037</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>TABLE 2.6</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>TABLE 2.6 Competitor analysis worksheet</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Identifying and Assessing Competitors</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>134</t>
         </is>
       </c>
-      <c r="F27" s="3" t="n">
+      <c r="F27" s="2" t="n">
         <v>149</v>
       </c>
-      <c r="G27" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="G27" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>P149-L001</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>TABLE 2.7</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>TABLE 2.7 Country Nomad higher education industry market analysis</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Higher Education Industry in Country Nomad</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>134</t>
         </is>
       </c>
-      <c r="F28" s="3" t="n">
+      <c r="F28" s="2" t="n">
         <v>149</v>
       </c>
-      <c r="G28" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="G28" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>P149-L038</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>TABLE 2.8</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>TABLE 2.8 Key questions for finance professionals to consider and answer</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>REVISITING THE ROLE OF THE CPA</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>139</t>
         </is>
       </c>
-      <c r="F29" s="3" t="n">
+      <c r="F29" s="2" t="n">
         <v>154</v>
       </c>
-      <c r="G29" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="G29" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>P154-L033</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>TABLE 2.8</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>TABLE 2.8 Concepts/models/approaches that can</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>be used to answer the key questions</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>140</t>
         </is>
       </c>
-      <c r="F30" s="3" t="n">
+      <c r="F30" s="2" t="n">
         <v>155</v>
       </c>
-      <c r="G30" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="G30" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>P155-L001</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>TABLE 2.9</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>TABLE 2.9 Top 10 global companies by market capitalisation, 2009 and 2019</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Competition Issues in the Digital Economy</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>140</t>
         </is>
       </c>
-      <c r="F31" s="3" t="n">
+      <c r="F31" s="2" t="n">
         <v>155</v>
       </c>
-      <c r="G31" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="G31" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>P155-L045</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>TABLE 3.1</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>TABLE 3.1 Pfizer stakeholder analysis</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Key Stakeholder Needs — Pfizer</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>151</t>
         </is>
       </c>
-      <c r="F32" s="3" t="n">
+      <c r="F32" s="2" t="n">
         <v>166</v>
       </c>
-      <c r="G32" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="G32" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>P166-L011</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>TABLE 3.1</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>TABLE 3.1 (continued)</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Examples of needs/requirements</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="F33" s="3" t="n">
+      <c r="F33" s="2" t="n">
         <v>167</v>
       </c>
-      <c r="G33" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="G33" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>P167-L001</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>TABLE 3.2</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>TABLE 3.2 Strategic alignment between goals and stakeholders — Cancer Council NSW</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>Strategy — Cancer Council NSW</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Alignment of Key Stakeholder Needs and Current Business Strategy — Cancer Council NSW</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>153</t>
         </is>
       </c>
-      <c r="F34" s="3" t="n">
+      <c r="F34" s="2" t="n">
         <v>168</v>
       </c>
-      <c r="G34" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="G34" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>P168-L001</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>TABLE 3.3</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>TABLE 3.3 Examples of industry, geographic markets, customers, and products and services</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>PRODUCTS AND SERVICES</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>165</t>
         </is>
       </c>
-      <c r="F35" s="3" t="n">
+      <c r="F35" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="G35" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="G35" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>P180-L001</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>TABLE 3.4</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>TABLE 3.4 Possible differentiation strategies</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Generic Strategy: Differentiation</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>169</t>
         </is>
       </c>
-      <c r="F36" s="3" t="n">
+      <c r="F36" s="2" t="n">
         <v>184</v>
       </c>
-      <c r="G36" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
+      <c r="G36" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>P184-L026</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>TABLE 3.4</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>TABLE 3.4 (continued)</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Comments</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>170</t>
         </is>
       </c>
-      <c r="F37" s="3" t="n">
+      <c r="F37" s="2" t="n">
         <v>185</v>
       </c>
-      <c r="G37" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="G37" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>P185-L001</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>TABLE 3.5</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>TABLE 3.5 Types of low-cost strategies</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Generic Strategy: Low Cost</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>171</t>
         </is>
       </c>
-      <c r="F38" s="3" t="n">
+      <c r="F38" s="2" t="n">
         <v>186</v>
       </c>
-      <c r="G38" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="G38" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>P186-L020</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>TABLE 3.5</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>TABLE 3.5 (continued)</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Comments</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>172</t>
         </is>
       </c>
-      <c r="F39" s="3" t="n">
+      <c r="F39" s="2" t="n">
         <v>187</v>
       </c>
-      <c r="G39" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="G39" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>P187-L001</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>TABLE 3.6</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>TABLE 3.6 Types of focus strategies</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Smiggle — A Focus Strategy</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>174</t>
         </is>
       </c>
-      <c r="F40" s="3" t="n">
+      <c r="F40" s="2" t="n">
         <v>189</v>
       </c>
-      <c r="G40" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
+      <c r="G40" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>P189-L017</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>TABLE 3.7</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>TABLE 3.7 Characteristics of effective performance measures</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>EFFECTIVE MEASUREMENT CRITERIA</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>177</t>
         </is>
       </c>
-      <c r="F41" s="3" t="n">
+      <c r="F41" s="2" t="n">
         <v>192</v>
       </c>
-      <c r="G41" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
+      <c r="G41" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>P192-L001</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>TABLE 3.8</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>TABLE 3.8 Examples of BSC measures</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Measures</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>181</t>
         </is>
       </c>
-      <c r="F42" s="3" t="n">
+      <c r="F42" s="2" t="n">
         <v>196</v>
       </c>
-      <c r="G42" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
+      <c r="G42" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>P196-L071</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>TABLE 3.8</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>TABLE 3.8 (continued)</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Data source</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>182</t>
         </is>
       </c>
-      <c r="F43" s="3" t="n">
+      <c r="F43" s="2" t="n">
         <v>197</v>
       </c>
-      <c r="G43" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
+      <c r="G43" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>P197-L001</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>TABLE 3.9</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>TABLE 3.9 Functions and related capabilities</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Exploration capability</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>190</t>
         </is>
       </c>
-      <c r="F44" s="3" t="n">
+      <c r="F44" s="2" t="n">
         <v>205</v>
       </c>
-      <c r="G44" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
+      <c r="G44" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>P205-L059</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>TABLE 3.10</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>TABLE 3.10 Key success factors for the pharmaceutical and toiletry wholesaling industry</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Strategic Capabilities</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>193</t>
         </is>
       </c>
-      <c r="F45" s="3" t="n">
+      <c r="F45" s="2" t="n">
         <v>208</v>
       </c>
-      <c r="G45" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
+      <c r="G45" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>P208-L021</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>TABLE 3.10</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>TABLE 3.10 (continued)</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>194</t>
         </is>
       </c>
-      <c r="F46" s="3" t="n">
+      <c r="F46" s="2" t="n">
         <v>209</v>
       </c>
-      <c r="G46" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
+      <c r="G46" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>P209-L001</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>TABLE 3.11</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>TABLE 3.11 SWOT analysis considerations</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>SWOT ANALYSIS</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>197</t>
         </is>
       </c>
-      <c r="F47" s="3" t="n">
+      <c r="F47" s="2" t="n">
         <v>212</v>
       </c>
-      <c r="G47" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
+      <c r="G47" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>P212-L033</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>TABLE 3.12</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>TABLE 3.12 Examples of SWOT analysis content</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Threats — sourced from external analysis</t>
         </is>
       </c>
-      <c r="E48" s="3" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>198</t>
         </is>
       </c>
-      <c r="F48" s="3" t="n">
+      <c r="F48" s="2" t="n">
         <v>213</v>
       </c>
-      <c r="G48" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
+      <c r="G48" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>P213-L002</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>TABLE 3.13</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>TABLE 3.13 Example of strategic questions to develop strategic options</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>Threats</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Examples of SWOT analysis content</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>198</t>
         </is>
       </c>
-      <c r="F49" s="3" t="n">
+      <c r="F49" s="2" t="n">
         <v>213</v>
       </c>
-      <c r="G49" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
+      <c r="G49" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>P213-L048</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>TABLE 3.14</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>TABLE 3.14 Gap analysis areas of focus</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Business strategy</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="F50" s="3" t="n">
+      <c r="F50" s="2" t="n">
         <v>215</v>
       </c>
-      <c r="G50" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
+      <c r="G50" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>P215-L001</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.1</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.1 Innovation groups and the 10 types of innovation</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>INNOVATION IN BUSINESS</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>210</t>
         </is>
       </c>
-      <c r="F51" s="3" t="n">
+      <c r="F51" s="2" t="n">
         <v>225</v>
       </c>
-      <c r="G51" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
+      <c r="G51" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>P225-L027</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.2</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.2 How Zara is applying the 10 types of innovation</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Zara is all about the Customer</t>
         </is>
       </c>
-      <c r="E52" s="3" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>212</t>
         </is>
       </c>
-      <c r="F52" s="3" t="n">
+      <c r="F52" s="2" t="n">
         <v>227</v>
       </c>
-      <c r="G52" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
+      <c r="G52" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>P227-L024</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.3</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.3 Extending the SWOT analysis to develop options</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>FOCUSING INNOVATION EFFORT</t>
         </is>
       </c>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>213</t>
         </is>
       </c>
-      <c r="F53" s="3" t="n">
+      <c r="F53" s="2" t="n">
         <v>228</v>
       </c>
-      <c r="G53" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H53" s="3" t="inlineStr">
+      <c r="G53" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>P228-L043</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.4</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.4 Reasons an organisation may divest</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>New service developmentis the outcome of design that:</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>216</t>
         </is>
       </c>
-      <c r="F54" s="3" t="n">
+      <c r="F54" s="2" t="n">
         <v>231</v>
       </c>
-      <c r="G54" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
+      <c r="G54" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>P231-L006</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.5</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.5 Customer segmentation and channels — Staples</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Staples, Inc. — Customer Market Expansion</t>
         </is>
       </c>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>222</t>
         </is>
       </c>
-      <c r="F55" s="3" t="n">
+      <c r="F55" s="2" t="n">
         <v>237</v>
       </c>
-      <c r="G55" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
+      <c r="G55" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>P237-L009</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.6</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.6 Arm &amp; Hammer’s Product Development history</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Arm &amp; Hammer — Product Development</t>
         </is>
       </c>
-      <c r="E56" s="3" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>224</t>
         </is>
       </c>
-      <c r="F56" s="3" t="n">
+      <c r="F56" s="2" t="n">
         <v>239</v>
       </c>
-      <c r="G56" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
+      <c r="G56" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>P239-L009</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.7</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.7 The key steps of a generic new product development process</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>THE NEW PRODUCT DEVELOPMENT PROCESS</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>227</t>
         </is>
       </c>
-      <c r="F57" s="3" t="n">
+      <c r="F57" s="2" t="n">
         <v>242</v>
       </c>
-      <c r="G57" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
+      <c r="G57" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>P242-L016</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.8</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.8 How Zara approaches the NPD process</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Zara — NPD Process</t>
         </is>
       </c>
-      <c r="E58" s="3" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>228</t>
         </is>
       </c>
-      <c r="F58" s="3" t="n">
+      <c r="F58" s="2" t="n">
         <v>243</v>
       </c>
-      <c r="G58" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H58" s="3" t="inlineStr">
+      <c r="G58" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>P243-L007</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="inlineStr">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.9</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.9 Summary of Kano’s performance attributes</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>attributes — Must be’s</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Threshold attributes — Must be’s</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>235</t>
         </is>
       </c>
-      <c r="F59" s="3" t="n">
+      <c r="F59" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="G59" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H59" s="3" t="inlineStr">
+      <c r="G59" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>P250-L001</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.10</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.10 The key components of service design</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>COMPONENTS OF SERVICE DESIGN</t>
         </is>
       </c>
-      <c r="E60" s="3" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>237</t>
         </is>
       </c>
-      <c r="F60" s="3" t="n">
+      <c r="F60" s="2" t="n">
         <v>252</v>
       </c>
-      <c r="G60" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
+      <c r="G60" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>P252-L034</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="inlineStr">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.10</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.10 (continued)</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>What to look for</t>
         </is>
       </c>
-      <c r="E61" s="3" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>238</t>
         </is>
       </c>
-      <c r="F61" s="3" t="n">
+      <c r="F61" s="2" t="n">
         <v>253</v>
       </c>
-      <c r="G61" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H61" s="3" t="inlineStr">
+      <c r="G61" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>P253-L001</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="inlineStr">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.11</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.11 Airbnb’s service design components</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Airbnb — Service Design</t>
         </is>
       </c>
-      <c r="E62" s="3" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>238</t>
         </is>
       </c>
-      <c r="F62" s="3" t="n">
+      <c r="F62" s="2" t="n">
         <v>253</v>
       </c>
-      <c r="G62" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
+      <c r="G62" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>P253-L037</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.12</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.12 The key stages of design thinking</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>DESIGN THINKING AND HUMAN-CENTRED DESIGN</t>
         </is>
       </c>
-      <c r="E63" s="3" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>242</t>
         </is>
       </c>
-      <c r="F63" s="3" t="n">
+      <c r="F63" s="2" t="n">
         <v>257</v>
       </c>
-      <c r="G63" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
+      <c r="G63" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>P257-L004</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.13</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.13 The Blue Ocean strategy process</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>raised well abovethe</t>
         </is>
       </c>
-      <c r="E64" s="3" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>247</t>
         </is>
       </c>
-      <c r="F64" s="3" t="n">
+      <c r="F64" s="2" t="n">
         <v>262</v>
       </c>
-      <c r="G64" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
+      <c r="G64" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>P262-L041</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="inlineStr">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.13</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.13 (continued)</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Process step</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>248</t>
         </is>
       </c>
-      <c r="F65" s="3" t="n">
+      <c r="F65" s="2" t="n">
         <v>263</v>
       </c>
-      <c r="G65" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H65" s="3" t="inlineStr">
+      <c r="G65" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>P263-L001</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.14</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.14 Cirque du Soleil key factors of competition</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Cirque du Soleil — Applying Blue Ocean Thinking</t>
         </is>
       </c>
-      <c r="E66" s="3" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>248</t>
         </is>
       </c>
-      <c r="F66" s="3" t="n">
+      <c r="F66" s="2" t="n">
         <v>263</v>
       </c>
-      <c r="G66" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
+      <c r="G66" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>P263-L042</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="inlineStr">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.15</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.15 Sample strategic objectives of market entry</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>from, for example, the external analysis conducted in module 2. Other reasons include access to resources,</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>OBJECTIVES OF MARKET ENTRY</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>258</t>
         </is>
       </c>
-      <c r="F67" s="3" t="n">
+      <c r="F67" s="2" t="n">
         <v>273</v>
       </c>
-      <c r="G67" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H67" s="3" t="inlineStr">
+      <c r="G67" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>P273-L017</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="inlineStr">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.16</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.16 Approaches to exporting</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Exporting</t>
         </is>
       </c>
-      <c r="E68" s="3" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>264</t>
         </is>
       </c>
-      <c r="F68" s="3" t="n">
+      <c r="F68" s="2" t="n">
         <v>279</v>
       </c>
-      <c r="G68" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
+      <c r="G68" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>P279-L023</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="inlineStr">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.17</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.17 M&amp;A guidelines</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Value of Mergers and Acquisitions</t>
         </is>
       </c>
-      <c r="E69" s="3" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>273</t>
         </is>
       </c>
-      <c r="F69" s="3" t="n">
+      <c r="F69" s="2" t="n">
         <v>288</v>
       </c>
-      <c r="G69" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H69" s="3" t="inlineStr">
+      <c r="G69" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>P288-L034</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="inlineStr">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.17</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.17 (continued)</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A success/failure</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>274</t>
         </is>
       </c>
-      <c r="F70" s="3" t="n">
+      <c r="F70" s="2" t="n">
         <v>289</v>
       </c>
-      <c r="G70" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
+      <c r="G70" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>P289-L001</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="inlineStr">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.18</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.18 Comparing various entry modes</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t>ENTRY MODES</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>ADVANTAGES AND DISADVANTAGES OF DIFFERENT ENTRY MODES</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>274</t>
         </is>
       </c>
-      <c r="F71" s="3" t="n">
+      <c r="F71" s="2" t="n">
         <v>289</v>
       </c>
-      <c r="G71" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H71" s="3" t="inlineStr">
+      <c r="G71" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>P289-L031</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="inlineStr">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.19</t>
         </is>
       </c>
-      <c r="B72" s="3" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.19 Summary of the characteristics, benefits and risks of each mode of entry</t>
         </is>
       </c>
-      <c r="C72" s="3" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D72" s="3" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>acquired</t>
         </is>
       </c>
-      <c r="E72" s="3" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>275</t>
         </is>
       </c>
-      <c r="F72" s="3" t="n">
+      <c r="F72" s="2" t="n">
         <v>290</v>
       </c>
-      <c r="G72" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
+      <c r="G72" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>P290-L046</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="inlineStr">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.19</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.19 (continued)</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D73" s="3" t="inlineStr">
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>ing</t>
         </is>
       </c>
-      <c r="E73" s="3" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>276</t>
         </is>
       </c>
-      <c r="F73" s="3" t="n">
+      <c r="F73" s="2" t="n">
         <v>291</v>
       </c>
-      <c r="G73" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H73" s="3" t="inlineStr">
+      <c r="G73" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>P291-L001</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="inlineStr">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.20</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.20 IDEO’s 10 faces of innovation personas</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D74" s="3" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>HARNESS</t>
         </is>
       </c>
-      <c r="E74" s="3" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>287</t>
         </is>
       </c>
-      <c r="F74" s="3" t="n">
+      <c r="F74" s="2" t="n">
         <v>302</v>
       </c>
-      <c r="G74" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
+      <c r="G74" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>P302-L012</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="inlineStr">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.21</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>TABLE 4.21 Key questions for finance professionals to consider and answer</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D75" s="3" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Open Innovation</t>
         </is>
       </c>
-      <c r="E75" s="3" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>289</t>
         </is>
       </c>
-      <c r="F75" s="3" t="n">
+      <c r="F75" s="2" t="n">
         <v>304</v>
       </c>
-      <c r="G75" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H75" s="3" t="inlineStr">
+      <c r="G75" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>P304-L015</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="inlineStr">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>TABLE 5.1</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>TABLE 5.1 Sample template for evaluating and comparing new strategic options</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
         <is>
           <t>MODULE 5</t>
         </is>
       </c>
-      <c r="D76" s="3" t="inlineStr">
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>WEIGHTED CRITERIA EVALUATION TOOL</t>
         </is>
       </c>
-      <c r="E76" s="3" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>315</t>
         </is>
       </c>
-      <c r="F76" s="3" t="n">
+      <c r="F76" s="2" t="n">
         <v>330</v>
       </c>
-      <c r="G76" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
+      <c r="G76" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>P330-L042</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>TABLE 5.1</t>
         </is>
       </c>
-      <c r="B77" s="3" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>TABLE 5.1 (continued)</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
         <is>
           <t>MODULE 5</t>
         </is>
       </c>
-      <c r="D77" s="3" t="inlineStr">
-        <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="inlineStr">
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Maximum points</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="F77" s="3" t="n">
+      <c r="F77" s="2" t="n">
         <v>331</v>
       </c>
-      <c r="G77" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H77" s="3" t="inlineStr">
+      <c r="G77" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>P331-L001</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="3" t="inlineStr">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>TABLE 5.2</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>TABLE 5.2 Weighted criteria evaluation tool</t>
         </is>
       </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
         <is>
           <t>MODULE 5</t>
         </is>
       </c>
-      <c r="D78" s="3" t="inlineStr">
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Weighted Criteria for Lululemon Athletica</t>
         </is>
       </c>
-      <c r="E78" s="3" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>317</t>
         </is>
       </c>
-      <c r="F78" s="3" t="n">
+      <c r="F78" s="2" t="n">
         <v>332</v>
       </c>
-      <c r="G78" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
+      <c r="G78" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>P332-L034</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="inlineStr">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>TABLE 5.2</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>TABLE 5.2 (continued)</t>
         </is>
       </c>
-      <c r="C79" s="3" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
         <is>
           <t>MODULE 5</t>
         </is>
       </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="inlineStr">
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Maximum points</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>318</t>
         </is>
       </c>
-      <c r="F79" s="3" t="n">
+      <c r="F79" s="2" t="n">
         <v>333</v>
       </c>
-      <c r="G79" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H79" s="3" t="inlineStr">
+      <c r="G79" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>P333-L001</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="3" t="inlineStr">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>TABLE 5.3</t>
         </is>
       </c>
-      <c r="B80" s="3" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>TABLE 5.3 Examples of strategic risks</t>
         </is>
       </c>
-      <c r="C80" s="3" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
         <is>
           <t>MODULE 5</t>
         </is>
       </c>
-      <c r="D80" s="3" t="inlineStr">
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Step 2: Determine Possible Causes</t>
         </is>
       </c>
-      <c r="E80" s="3" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>323</t>
         </is>
       </c>
-      <c r="F80" s="3" t="n">
+      <c r="F80" s="2" t="n">
         <v>338</v>
       </c>
-      <c r="G80" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H80" s="3" t="inlineStr">
+      <c r="G80" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>P338-L001</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="inlineStr">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>TABLE 5.4</t>
         </is>
       </c>
-      <c r="B81" s="3" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>TABLE 5.4 Consequence rating matrix</t>
         </is>
       </c>
-      <c r="C81" s="3" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
         <is>
           <t>MODULE 5</t>
         </is>
       </c>
-      <c r="D81" s="3" t="inlineStr">
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Step 3: Determine Possible Consequences</t>
         </is>
       </c>
-      <c r="E81" s="3" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>323</t>
         </is>
       </c>
-      <c r="F81" s="3" t="n">
+      <c r="F81" s="2" t="n">
         <v>338</v>
       </c>
-      <c r="G81" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H81" s="3" t="inlineStr">
+      <c r="G81" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>P338-L056</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="3" t="inlineStr">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>TABLE 5.4</t>
         </is>
       </c>
-      <c r="B82" s="3" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>TABLE 5.4 (continued)</t>
         </is>
       </c>
-      <c r="C82" s="3" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
         <is>
           <t>MODULE 5</t>
         </is>
       </c>
-      <c r="D82" s="3" t="inlineStr">
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>image/reputation</t>
         </is>
       </c>
-      <c r="E82" s="3" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>324</t>
         </is>
       </c>
-      <c r="F82" s="3" t="n">
+      <c r="F82" s="2" t="n">
         <v>339</v>
       </c>
-      <c r="G82" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H82" s="3" t="inlineStr">
+      <c r="G82" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>P339-L001</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="inlineStr">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>TABLE 5.5</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>TABLE 5.5 Inherent risk table</t>
         </is>
       </c>
-      <c r="C83" s="3" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
         <is>
           <t>MODULE 5</t>
         </is>
       </c>
-      <c r="D83" s="3" t="inlineStr">
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Step 5: Determine Risk Rating</t>
         </is>
       </c>
-      <c r="E83" s="3" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>324</t>
         </is>
       </c>
-      <c r="F83" s="3" t="n">
+      <c r="F83" s="2" t="n">
         <v>339</v>
       </c>
-      <c r="G83" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H83" s="3" t="inlineStr">
+      <c r="G83" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>P339-L091</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="inlineStr">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>TABLE 5.6</t>
         </is>
       </c>
-      <c r="B84" s="3" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>TABLE 5.6 Risk of a fire at MOSM</t>
         </is>
       </c>
-      <c r="C84" s="3" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
         <is>
           <t>MODULE 5</t>
         </is>
       </c>
-      <c r="D84" s="3" t="inlineStr">
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>MOSM Risk Rating</t>
         </is>
       </c>
-      <c r="E84" s="3" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>325</t>
         </is>
       </c>
-      <c r="F84" s="3" t="n">
+      <c r="F84" s="2" t="n">
         <v>340</v>
       </c>
-      <c r="G84" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
+      <c r="G84" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>P340-L010</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="inlineStr">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>TABLE 5.7</t>
         </is>
       </c>
-      <c r="B85" s="3" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>TABLE 5.7 Risk of a dissatisfied school group leader</t>
         </is>
       </c>
-      <c r="C85" s="3" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
         <is>
           <t>MODULE 5</t>
         </is>
       </c>
-      <c r="D85" s="3" t="inlineStr">
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E85" s="3" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>325</t>
         </is>
       </c>
-      <c r="F85" s="3" t="n">
+      <c r="F85" s="2" t="n">
         <v>340</v>
       </c>
-      <c r="G85" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H85" s="3" t="inlineStr">
+      <c r="G85" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>P340-L049</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="3" t="inlineStr">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>TABLE 5.8</t>
         </is>
       </c>
-      <c r="B86" s="3" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>TABLE 5.8 MOSM’s broad strategic options (themes)</t>
         </is>
       </c>
-      <c r="C86" s="3" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
         <is>
           <t>MODULE 5</t>
         </is>
       </c>
-      <c r="D86" s="3" t="inlineStr">
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>MOSM — Grouping Strategic Options</t>
         </is>
       </c>
-      <c r="E86" s="3" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>332</t>
         </is>
       </c>
-      <c r="F86" s="3" t="n">
+      <c r="F86" s="2" t="n">
         <v>347</v>
       </c>
-      <c r="G86" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H86" s="3" t="inlineStr">
+      <c r="G86" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>P347-L001</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="3" t="inlineStr">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>TABLE 5.9</t>
         </is>
       </c>
-      <c r="B87" s="3" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>TABLE 5.9 Checklist for external consistency</t>
         </is>
       </c>
-      <c r="C87" s="3" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
         <is>
           <t>MODULE 5</t>
         </is>
       </c>
-      <c r="D87" s="3" t="inlineStr">
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>External Consistency</t>
         </is>
       </c>
-      <c r="E87" s="3" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>333</t>
         </is>
       </c>
-      <c r="F87" s="3" t="n">
+      <c r="F87" s="2" t="n">
         <v>348</v>
       </c>
-      <c r="G87" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H87" s="3" t="inlineStr">
+      <c r="G87" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>P348-L001</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="inlineStr">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>TABLE 5.10</t>
         </is>
       </c>
-      <c r="B88" s="3" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>TABLE 5.10 Checklist for internal consistency</t>
         </is>
       </c>
-      <c r="C88" s="3" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
         <is>
           <t>MODULE 5</t>
         </is>
       </c>
-      <c r="D88" s="3" t="inlineStr">
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Internal Consistency</t>
         </is>
       </c>
-      <c r="E88" s="3" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>334</t>
         </is>
       </c>
-      <c r="F88" s="3" t="n">
+      <c r="F88" s="2" t="n">
         <v>349</v>
       </c>
-      <c r="G88" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H88" s="3" t="inlineStr">
+      <c r="G88" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>P349-L024</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="inlineStr">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>TABLE 5.11</t>
         </is>
       </c>
-      <c r="B89" s="3" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>TABLE 5.11 Checklist for feasibility</t>
         </is>
       </c>
-      <c r="C89" s="3" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
         <is>
           <t>MODULE 5</t>
         </is>
       </c>
-      <c r="D89" s="3" t="inlineStr">
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Feasibility</t>
         </is>
       </c>
-      <c r="E89" s="3" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>335</t>
         </is>
       </c>
-      <c r="F89" s="3" t="n">
+      <c r="F89" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="G89" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H89" s="3" t="inlineStr">
+      <c r="G89" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>P350-L026</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="3" t="inlineStr">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>TABLE 5.11</t>
         </is>
       </c>
-      <c r="B90" s="3" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>TABLE 5.11 (continued)</t>
         </is>
       </c>
-      <c r="C90" s="3" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
         <is>
           <t>MODULE 5</t>
         </is>
       </c>
-      <c r="D90" s="3" t="inlineStr">
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Typical questions to ask</t>
         </is>
       </c>
-      <c r="E90" s="3" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="F90" s="3" t="n">
+      <c r="F90" s="2" t="n">
         <v>351</v>
       </c>
-      <c r="G90" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H90" s="3" t="inlineStr">
+      <c r="G90" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>P351-L001</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="3" t="inlineStr">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>TABLE 5.12</t>
         </is>
       </c>
-      <c r="B91" s="3" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>TABLE 5.12 Checklist for competitive advantage</t>
         </is>
       </c>
-      <c r="C91" s="3" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
         <is>
           <t>MODULE 5</t>
         </is>
       </c>
-      <c r="D91" s="3" t="inlineStr">
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Competitive Advantage</t>
         </is>
       </c>
-      <c r="E91" s="3" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="F91" s="3" t="n">
+      <c r="F91" s="2" t="n">
         <v>351</v>
       </c>
-      <c r="G91" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H91" s="3" t="inlineStr">
+      <c r="G91" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>P351-L037</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="inlineStr">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>TABLE 5.13</t>
         </is>
       </c>
-      <c r="B92" s="3" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>TABLE 5.13 Key questions for strategy development</t>
         </is>
       </c>
-      <c r="C92" s="3" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
         <is>
           <t>MODULE 5</t>
         </is>
       </c>
-      <c r="D92" s="3" t="inlineStr">
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>REVIEWING THE STRATEGY</t>
         </is>
       </c>
-      <c r="E92" s="3" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>342</t>
         </is>
       </c>
-      <c r="F92" s="3" t="n">
+      <c r="F92" s="2" t="n">
         <v>357</v>
       </c>
-      <c r="G92" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H92" s="3" t="inlineStr">
+      <c r="G92" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>P357-L027</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="inlineStr">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>TABLE 6.1</t>
         </is>
       </c>
-      <c r="B93" s="3" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>TABLE 6.1 Application for the McKinsey 7-S tool</t>
         </is>
       </c>
-      <c r="C93" s="3" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
         <is>
           <t>MODULE 6</t>
         </is>
       </c>
-      <c r="D93" s="3" t="inlineStr">
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>values</t>
         </is>
       </c>
-      <c r="E93" s="3" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>365</t>
         </is>
       </c>
-      <c r="F93" s="3" t="n">
+      <c r="F93" s="2" t="n">
         <v>380</v>
       </c>
-      <c r="G93" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H93" s="3" t="inlineStr">
+      <c r="G93" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>P380-L033</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="3" t="inlineStr">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>TABLE 6.2</t>
         </is>
       </c>
-      <c r="B94" s="3" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>TABLE 6.2 Zara systems analysis</t>
         </is>
       </c>
-      <c r="C94" s="3" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
         <is>
           <t>MODULE 6</t>
         </is>
       </c>
-      <c r="D94" s="3" t="inlineStr">
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Zara’s Systems and Implementation Prowess</t>
         </is>
       </c>
-      <c r="E94" s="3" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>376</t>
         </is>
       </c>
-      <c r="F94" s="3" t="n">
+      <c r="F94" s="2" t="n">
         <v>391</v>
       </c>
-      <c r="G94" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H94" s="3" t="inlineStr">
+      <c r="G94" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>P391-L017</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="3" t="inlineStr">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>TABLE 6.3</t>
         </is>
       </c>
-      <c r="B95" s="3" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>TABLE 6.3 Key distinctions between projects and programs</t>
         </is>
       </c>
-      <c r="C95" s="3" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
         <is>
           <t>MODULE 6</t>
         </is>
       </c>
-      <c r="D95" s="3" t="inlineStr">
-        <is>
-          <t>The Museum of Sports Memorabilia (MOSM) example from module 5 shows how individual projects</t>
-        </is>
-      </c>
-      <c r="E95" s="3" t="inlineStr">
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>PROJECT AND PROGRAM MANAGEMENT</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>390</t>
         </is>
       </c>
-      <c r="F95" s="3" t="n">
+      <c r="F95" s="2" t="n">
         <v>405</v>
       </c>
-      <c r="G95" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H95" s="3" t="inlineStr">
+      <c r="G95" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>P405-L023</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="3" t="inlineStr">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>TABLE 6.4</t>
         </is>
       </c>
-      <c r="B96" s="3" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>TABLE 6.4 Reasons implementation can fail</t>
         </is>
       </c>
-      <c r="C96" s="3" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
         <is>
           <t>MODULE 6</t>
         </is>
       </c>
-      <c r="D96" s="3" t="inlineStr">
-        <is>
-          <t>AND MANAGEMENT</t>
-        </is>
-      </c>
-      <c r="E96" s="3" t="inlineStr">
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>6.6 FURTHER IMPLICATIONS FOR LEADERSHIP AND MANAGEMENT</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>402</t>
         </is>
       </c>
-      <c r="F96" s="3" t="n">
+      <c r="F96" s="2" t="n">
         <v>417</v>
       </c>
-      <c r="G96" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H96" s="3" t="inlineStr">
+      <c r="G96" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>P417-L034</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="inlineStr">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>TABLE 6.5</t>
         </is>
       </c>
-      <c r="B97" s="3" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>TABLE 6.5 implementation</t>
         </is>
       </c>
-      <c r="C97" s="3" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
         <is>
           <t>MODULE 6</t>
         </is>
       </c>
-      <c r="D97" s="3" t="inlineStr">
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Key questions for finance professionals to consider and answer regarding strategy</t>
         </is>
       </c>
-      <c r="E97" s="3" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>411</t>
         </is>
       </c>
-      <c r="F97" s="3" t="n">
+      <c r="F97" s="2" t="n">
         <v>426</v>
       </c>
-      <c r="G97" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H97" s="3" t="inlineStr">
+      <c r="G97" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>P426-L001</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="3" t="inlineStr">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>TABLE 7.1</t>
         </is>
       </c>
-      <c r="B98" s="3" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>TABLE 7.1 Technologies with transformative potential</t>
         </is>
       </c>
-      <c r="C98" s="3" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="D98" s="3" t="inlineStr">
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="E98" s="3" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>420</t>
         </is>
       </c>
-      <c r="F98" s="3" t="n">
+      <c r="F98" s="2" t="n">
         <v>435</v>
       </c>
-      <c r="G98" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H98" s="3" t="inlineStr">
+      <c r="G98" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>P435-L014</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="inlineStr">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>TABLE 7.2</t>
         </is>
       </c>
-      <c r="B99" s="3" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>TABLE 7.2 The free model</t>
         </is>
       </c>
-      <c r="C99" s="3" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="D99" s="3" t="inlineStr">
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>The Free Model</t>
         </is>
       </c>
-      <c r="E99" s="3" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>436</t>
         </is>
       </c>
-      <c r="F99" s="3" t="n">
+      <c r="F99" s="2" t="n">
         <v>451</v>
       </c>
-      <c r="G99" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H99" s="3" t="inlineStr">
+      <c r="G99" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>P451-L001</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="3" t="inlineStr">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>TABLE 7.3</t>
         </is>
       </c>
-      <c r="B100" s="3" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>TABLE 7.3 Potential applications of advanced manufacturing technologies</t>
         </is>
       </c>
-      <c r="C100" s="3" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="D100" s="3" t="inlineStr">
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Advanced Manufacturing</t>
         </is>
       </c>
-      <c r="E100" s="3" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>443</t>
         </is>
       </c>
-      <c r="F100" s="3" t="n">
+      <c r="F100" s="2" t="n">
         <v>458</v>
       </c>
-      <c r="G100" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H100" s="3" t="inlineStr">
+      <c r="G100" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>P458-L022</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="3" t="inlineStr">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>TABLE 7.4</t>
         </is>
       </c>
-      <c r="B101" s="3" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>TABLE 7.4 Principles for managing through disruption</t>
         </is>
       </c>
-      <c r="C101" s="3" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="D101" s="3" t="inlineStr">
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>DISRUPTION AND STRATEGIC INNOVATION</t>
         </is>
       </c>
-      <c r="E101" s="3" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>453</t>
         </is>
       </c>
-      <c r="F101" s="3" t="n">
+      <c r="F101" s="2" t="n">
         <v>468</v>
       </c>
-      <c r="G101" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H101" s="3" t="inlineStr">
+      <c r="G101" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>P468-L011</t>
         </is>
